--- a/data.mn/public/datasets/heating-energy.xlsx
+++ b/data.mn/public/datasets/heating-energy.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,407 +414,2133 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF4"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Indicator</t>
+          <t>year</t>
         </is>
       </c>
-      <c r="B1" t="n">
-        <v>1995</v>
-      </c>
-      <c r="C1" t="n">
-        <v>1996</v>
-      </c>
-      <c r="D1" t="n">
-        <v>1997</v>
-      </c>
-      <c r="E1" t="n">
-        <v>1998</v>
-      </c>
-      <c r="F1" t="n">
-        <v>1999</v>
-      </c>
-      <c r="G1" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H1" t="n">
-        <v>2001</v>
-      </c>
-      <c r="I1" t="n">
-        <v>2002</v>
-      </c>
-      <c r="J1" t="n">
-        <v>2003</v>
-      </c>
-      <c r="K1" t="n">
-        <v>2004</v>
-      </c>
-      <c r="L1" t="n">
-        <v>2005</v>
-      </c>
-      <c r="M1" t="n">
-        <v>2006</v>
-      </c>
-      <c r="N1" t="n">
-        <v>2007</v>
-      </c>
-      <c r="O1" t="n">
-        <v>2008</v>
-      </c>
-      <c r="P1" t="n">
-        <v>2009</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>2010</v>
-      </c>
-      <c r="R1" t="n">
-        <v>2011</v>
-      </c>
-      <c r="S1" t="n">
-        <v>2012</v>
-      </c>
-      <c r="T1" t="n">
-        <v>2013</v>
-      </c>
-      <c r="U1" t="n">
-        <v>2014</v>
-      </c>
-      <c r="V1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="W1" t="n">
-        <v>2016</v>
-      </c>
-      <c r="X1" t="n">
-        <v>2017</v>
-      </c>
-      <c r="Y1" t="n">
-        <v>2018</v>
-      </c>
-      <c r="Z1" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AA1" t="n">
-        <v>2020</v>
-      </c>
-      <c r="AB1" t="n">
-        <v>2021</v>
-      </c>
-      <c r="AC1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AD1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AE1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AF1" t="n">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
         <is>
           <t>Distribution total</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>6772</v>
-      </c>
-      <c r="C2" t="n">
-        <v>6115</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5997</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5769</v>
-      </c>
-      <c r="F2" t="n">
-        <v>6410</v>
-      </c>
-      <c r="G2" t="n">
-        <v>6514</v>
-      </c>
-      <c r="H2" t="n">
-        <v>6419</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6569</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6583</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7087</v>
-      </c>
-      <c r="L2" t="n">
-        <v>7180</v>
-      </c>
-      <c r="M2" t="n">
-        <v>7271</v>
-      </c>
-      <c r="N2" t="n">
-        <v>7165</v>
-      </c>
-      <c r="O2" t="n">
-        <v>7238</v>
-      </c>
-      <c r="P2" t="n">
-        <v>7829</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>7820</v>
-      </c>
-      <c r="R2" t="n">
-        <v>8033</v>
-      </c>
-      <c r="S2" t="n">
-        <v>8693</v>
-      </c>
-      <c r="T2" t="n">
-        <v>8672</v>
-      </c>
-      <c r="U2" t="n">
-        <v>9163</v>
-      </c>
-      <c r="V2" t="n">
-        <v>9707</v>
-      </c>
-      <c r="W2" t="n">
-        <v>9915</v>
-      </c>
-      <c r="X2" t="n">
-        <v>10254</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>10640</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>11108</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>12191</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>13012</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>13596</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>14354</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>15314</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>16566</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Gross generation</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>6832</v>
-      </c>
-      <c r="C3" t="n">
-        <v>6497</v>
-      </c>
-      <c r="D3" t="n">
-        <v>6551</v>
-      </c>
-      <c r="E3" t="n">
-        <v>6722</v>
-      </c>
-      <c r="F3" t="n">
-        <v>6762</v>
-      </c>
-      <c r="G3" t="n">
-        <v>6885</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6597</v>
-      </c>
-      <c r="I3" t="n">
-        <v>6868</v>
-      </c>
-      <c r="J3" t="n">
-        <v>7133</v>
-      </c>
-      <c r="K3" t="n">
-        <v>7747</v>
-      </c>
-      <c r="L3" t="n">
-        <v>7806</v>
-      </c>
-      <c r="M3" t="n">
-        <v>7850</v>
-      </c>
-      <c r="N3" t="n">
-        <v>7724</v>
-      </c>
-      <c r="O3" t="n">
-        <v>7760</v>
-      </c>
-      <c r="P3" t="n">
-        <v>8321</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>8363</v>
-      </c>
-      <c r="R3" t="n">
-        <v>8683</v>
-      </c>
-      <c r="S3" t="n">
-        <v>9322</v>
-      </c>
-      <c r="T3" t="n">
-        <v>9512</v>
-      </c>
-      <c r="U3" t="n">
-        <v>10032</v>
-      </c>
-      <c r="V3" t="n">
-        <v>10680</v>
-      </c>
-      <c r="W3" t="n">
-        <v>10799</v>
-      </c>
-      <c r="X3" t="n">
-        <v>11296</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>12505</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>13277</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>14122</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>14973</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>15643</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>16394</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>17383</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>18632</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Household and communal housing</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Industry and construction</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Station internal use</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>Transmission losses</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Transport and communication</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B2" t="n">
+        <v>147</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6772</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6832</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2361</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2709</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1110</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41</v>
+      </c>
+      <c r="I2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J2" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6115</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6497</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3332</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1784</v>
+      </c>
+      <c r="G3" t="n">
+        <v>648</v>
+      </c>
+      <c r="H3" t="n">
+        <v>316</v>
+      </c>
+      <c r="I3" t="n">
+        <v>66</v>
+      </c>
+      <c r="J3" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1997</v>
+      </c>
       <c r="B4" t="n">
+        <v>46</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5997</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6551</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3126</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1778</v>
+      </c>
+      <c r="G4" t="n">
+        <v>796</v>
+      </c>
+      <c r="H4" t="n">
+        <v>528</v>
+      </c>
+      <c r="I4" t="n">
+        <v>27</v>
+      </c>
+      <c r="J4" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B5" t="n">
+        <v>327</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5769</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6722</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2743</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1730</v>
+      </c>
+      <c r="G5" t="n">
+        <v>769</v>
+      </c>
+      <c r="H5" t="n">
+        <v>733</v>
+      </c>
+      <c r="I5" t="n">
+        <v>220</v>
+      </c>
+      <c r="J5" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B6" t="n">
+        <v>49</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6410</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6762</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3235</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1995</v>
+      </c>
+      <c r="G6" t="n">
+        <v>696</v>
+      </c>
+      <c r="H6" t="n">
+        <v>75</v>
+      </c>
+      <c r="I6" t="n">
+        <v>277</v>
+      </c>
+      <c r="J6" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B7" t="n">
+        <v>33</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6514</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6885</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2655</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2620</v>
+      </c>
+      <c r="G7" t="n">
+        <v>795</v>
+      </c>
+      <c r="H7" t="n">
+        <v>138</v>
+      </c>
+      <c r="I7" t="n">
+        <v>233</v>
+      </c>
+      <c r="J7" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B8" t="n">
+        <v>37</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6419</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6597</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2991</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2344</v>
+      </c>
+      <c r="G8" t="n">
+        <v>563</v>
+      </c>
+      <c r="H8" t="n">
+        <v>60</v>
+      </c>
+      <c r="I8" t="n">
+        <v>119</v>
+      </c>
+      <c r="J8" t="n">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6569</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6868</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2843</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2429</v>
+      </c>
+      <c r="G9" t="n">
+        <v>842</v>
+      </c>
+      <c r="H9" t="n">
+        <v>145</v>
+      </c>
+      <c r="I9" t="n">
+        <v>154</v>
+      </c>
+      <c r="J9" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B10" t="n">
+        <v>74</v>
+      </c>
+      <c r="C10" t="n">
+        <v>6583</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7133</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2753</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1831</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1504</v>
+      </c>
+      <c r="H10" t="n">
+        <v>336</v>
+      </c>
+      <c r="I10" t="n">
+        <v>214</v>
+      </c>
+      <c r="J10" t="n">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B11" t="n">
+        <v>77</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7087</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7747</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1468</v>
+      </c>
+      <c r="H11" t="n">
+        <v>480</v>
+      </c>
+      <c r="I11" t="n">
+        <v>180</v>
+      </c>
+      <c r="J11" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B12" t="n">
+        <v>71</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7180</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7806</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3051</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2276</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1375</v>
+      </c>
+      <c r="H12" t="n">
+        <v>447</v>
+      </c>
+      <c r="I12" t="n">
+        <v>179</v>
+      </c>
+      <c r="J12" t="n">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B13" t="n">
+        <v>40</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7271</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7850</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3355</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1568</v>
+      </c>
+      <c r="H13" t="n">
+        <v>435</v>
+      </c>
+      <c r="I13" t="n">
+        <v>145</v>
+      </c>
+      <c r="J13" t="n">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B14" t="n">
+        <v>38</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7165</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7724</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3372</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2068</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1401</v>
+      </c>
+      <c r="H14" t="n">
+        <v>415</v>
+      </c>
+      <c r="I14" t="n">
+        <v>144</v>
+      </c>
+      <c r="J14" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B15" t="n">
+        <v>40</v>
+      </c>
+      <c r="C15" t="n">
+        <v>7238</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7760</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3430</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2168</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1322</v>
+      </c>
+      <c r="H15" t="n">
+        <v>397</v>
+      </c>
+      <c r="I15" t="n">
+        <v>125</v>
+      </c>
+      <c r="J15" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B16" t="n">
+        <v>38</v>
+      </c>
+      <c r="C16" t="n">
+        <v>7829</v>
+      </c>
+      <c r="D16" t="n">
+        <v>8321</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3574</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2002</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1950</v>
+      </c>
+      <c r="H16" t="n">
+        <v>335</v>
+      </c>
+      <c r="I16" t="n">
+        <v>157</v>
+      </c>
+      <c r="J16" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B17" t="n">
+        <v>41</v>
+      </c>
+      <c r="C17" t="n">
+        <v>7820</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8363</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2083</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2053</v>
+      </c>
+      <c r="H17" t="n">
+        <v>338</v>
+      </c>
+      <c r="I17" t="n">
+        <v>204</v>
+      </c>
+      <c r="J17" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B18" t="n">
+        <v>43</v>
+      </c>
+      <c r="C18" t="n">
+        <v>8033</v>
+      </c>
+      <c r="D18" t="n">
+        <v>8683</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3474</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2067</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2170</v>
+      </c>
+      <c r="H18" t="n">
+        <v>366</v>
+      </c>
+      <c r="I18" t="n">
+        <v>284</v>
+      </c>
+      <c r="J18" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B19" t="n">
+        <v>33</v>
+      </c>
+      <c r="C19" t="n">
+        <v>8693</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9322</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3737</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2109</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2533</v>
+      </c>
+      <c r="H19" t="n">
+        <v>379</v>
+      </c>
+      <c r="I19" t="n">
+        <v>250</v>
+      </c>
+      <c r="J19" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B20" t="n">
+        <v>49</v>
+      </c>
+      <c r="C20" t="n">
+        <v>8672</v>
+      </c>
+      <c r="D20" t="n">
+        <v>9512</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3819</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2162</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2333</v>
+      </c>
+      <c r="H20" t="n">
+        <v>523</v>
+      </c>
+      <c r="I20" t="n">
+        <v>318</v>
+      </c>
+      <c r="J20" t="n">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B21" t="n">
+        <v>43</v>
+      </c>
+      <c r="C21" t="n">
+        <v>9163</v>
+      </c>
+      <c r="D21" t="n">
+        <v>10032</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3930</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2177</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2713</v>
+      </c>
+      <c r="H21" t="n">
+        <v>537</v>
+      </c>
+      <c r="I21" t="n">
+        <v>333</v>
+      </c>
+      <c r="J21" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B22" t="n">
+        <v>48</v>
+      </c>
+      <c r="C22" t="n">
+        <v>9707</v>
+      </c>
+      <c r="D22" t="n">
+        <v>10680</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4040</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2359</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2945</v>
+      </c>
+      <c r="H22" t="n">
+        <v>647</v>
+      </c>
+      <c r="I22" t="n">
+        <v>325</v>
+      </c>
+      <c r="J22" t="n">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B23" t="n">
+        <v>48</v>
+      </c>
+      <c r="C23" t="n">
+        <v>9915</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10799</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4110</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2365</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3034</v>
+      </c>
+      <c r="H23" t="n">
+        <v>565</v>
+      </c>
+      <c r="I23" t="n">
+        <v>319</v>
+      </c>
+      <c r="J23" t="n">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B24" t="n">
+        <v>51</v>
+      </c>
+      <c r="C24" t="n">
+        <v>10254</v>
+      </c>
+      <c r="D24" t="n">
+        <v>11296</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3868</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2498</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3488</v>
+      </c>
+      <c r="H24" t="n">
+        <v>552</v>
+      </c>
+      <c r="I24" t="n">
+        <v>490</v>
+      </c>
+      <c r="J24" t="n">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B25" t="n">
+        <v>55</v>
+      </c>
+      <c r="C25" t="n">
+        <v>10640</v>
+      </c>
+      <c r="D25" t="n">
+        <v>12505</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4104</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2912</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3219</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1375</v>
+      </c>
+      <c r="I25" t="n">
+        <v>490</v>
+      </c>
+      <c r="J25" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B26" t="n">
+        <v>53</v>
+      </c>
+      <c r="C26" t="n">
+        <v>11108</v>
+      </c>
+      <c r="D26" t="n">
+        <v>13277</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4073</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2914</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3741</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1603</v>
+      </c>
+      <c r="I26" t="n">
+        <v>567</v>
+      </c>
+      <c r="J26" t="n">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57</v>
+      </c>
+      <c r="C27" t="n">
+        <v>12191</v>
+      </c>
+      <c r="D27" t="n">
+        <v>14122</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4517</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3178</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4055</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1312</v>
+      </c>
+      <c r="I27" t="n">
+        <v>619</v>
+      </c>
+      <c r="J27" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58</v>
+      </c>
+      <c r="C28" t="n">
+        <v>13012</v>
+      </c>
+      <c r="D28" t="n">
+        <v>14973</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4261</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3410</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4879</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1405</v>
+      </c>
+      <c r="I28" t="n">
+        <v>556</v>
+      </c>
+      <c r="J28" t="n">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B29" t="n">
+        <v>71</v>
+      </c>
+      <c r="C29" t="n">
+        <v>13596</v>
+      </c>
+      <c r="D29" t="n">
+        <v>15643</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4683</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3472</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4943</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1485</v>
+      </c>
+      <c r="I29" t="n">
+        <v>563</v>
+      </c>
+      <c r="J29" t="n">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B30" t="n">
+        <v>65</v>
+      </c>
+      <c r="C30" t="n">
+        <v>14354</v>
+      </c>
+      <c r="D30" t="n">
+        <v>16394</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5174</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3602</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5077</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1483</v>
+      </c>
+      <c r="I30" t="n">
+        <v>556</v>
+      </c>
+      <c r="J30" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B31" t="n">
+        <v>86</v>
+      </c>
+      <c r="C31" t="n">
+        <v>15314</v>
+      </c>
+      <c r="D31" t="n">
+        <v>17383</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5460</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3530</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5764</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1530</v>
+      </c>
+      <c r="I31" t="n">
+        <v>539</v>
+      </c>
+      <c r="J31" t="n">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90</v>
+      </c>
+      <c r="C32" t="n">
+        <v>16566</v>
+      </c>
+      <c r="D32" t="n">
+        <v>18632</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5482</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3758</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6723</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1509</v>
+      </c>
+      <c r="I32" t="n">
+        <v>558</v>
+      </c>
+      <c r="J32" t="n">
+        <v>513</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ААНБ болон өрхөд түгээсэн-Бүгд</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Бусад</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Дулааны цахилгаан станцын дотоод хэрэглээ</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Тээвэр, холбоо</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Түгээлтийн алдагдал</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Хөдөө аж ахуй</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Үйлдвэр, барилга</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Үйлдвэрлэсэн</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Өрх, орон сууц, нийтийн аж ахуй</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B2" t="n">
+        <v>6772</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1110</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41</v>
+      </c>
+      <c r="E2" t="n">
+        <v>446</v>
+      </c>
+      <c r="F2" t="n">
         <v>18</v>
       </c>
+      <c r="G2" t="n">
+        <v>147</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2709</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6832</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B3" t="n">
+        <v>6115</v>
+      </c>
+      <c r="C3" t="n">
+        <v>648</v>
+      </c>
+      <c r="D3" t="n">
+        <v>316</v>
+      </c>
+      <c r="E3" t="n">
+        <v>249</v>
+      </c>
+      <c r="F3" t="n">
+        <v>66</v>
+      </c>
+      <c r="G3" t="n">
+        <v>103</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1784</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6497</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3332</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5997</v>
+      </c>
       <c r="C4" t="n">
-        <v>66</v>
+        <v>796</v>
       </c>
       <c r="D4" t="n">
+        <v>528</v>
+      </c>
+      <c r="E4" t="n">
+        <v>250</v>
+      </c>
+      <c r="F4" t="n">
         <v>27</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
+        <v>46</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1778</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6551</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3126</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5769</v>
+      </c>
+      <c r="C5" t="n">
+        <v>769</v>
+      </c>
+      <c r="D5" t="n">
+        <v>733</v>
+      </c>
+      <c r="E5" t="n">
+        <v>202</v>
+      </c>
+      <c r="F5" t="n">
         <v>220</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G5" t="n">
+        <v>327</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1730</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6722</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2743</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B6" t="n">
+        <v>6410</v>
+      </c>
+      <c r="C6" t="n">
+        <v>696</v>
+      </c>
+      <c r="D6" t="n">
+        <v>75</v>
+      </c>
+      <c r="E6" t="n">
+        <v>435</v>
+      </c>
+      <c r="F6" t="n">
         <v>277</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G6" t="n">
+        <v>49</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1995</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6762</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B7" t="n">
+        <v>6514</v>
+      </c>
+      <c r="C7" t="n">
+        <v>795</v>
+      </c>
+      <c r="D7" t="n">
+        <v>138</v>
+      </c>
+      <c r="E7" t="n">
+        <v>411</v>
+      </c>
+      <c r="F7" t="n">
         <v>233</v>
       </c>
-      <c r="H4" t="n">
+      <c r="G7" t="n">
+        <v>33</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2620</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6885</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6419</v>
+      </c>
+      <c r="C8" t="n">
+        <v>563</v>
+      </c>
+      <c r="D8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E8" t="n">
+        <v>486</v>
+      </c>
+      <c r="F8" t="n">
         <v>119</v>
       </c>
-      <c r="I4" t="n">
+      <c r="G8" t="n">
+        <v>37</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2344</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6597</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2991</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B9" t="n">
+        <v>6569</v>
+      </c>
+      <c r="C9" t="n">
+        <v>842</v>
+      </c>
+      <c r="D9" t="n">
+        <v>145</v>
+      </c>
+      <c r="E9" t="n">
+        <v>420</v>
+      </c>
+      <c r="F9" t="n">
         <v>154</v>
       </c>
-      <c r="J4" t="n">
+      <c r="G9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2429</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6868</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B10" t="n">
+        <v>6583</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1504</v>
+      </c>
+      <c r="D10" t="n">
+        <v>336</v>
+      </c>
+      <c r="E10" t="n">
+        <v>421</v>
+      </c>
+      <c r="F10" t="n">
         <v>214</v>
       </c>
-      <c r="K4" t="n">
+      <c r="G10" t="n">
+        <v>74</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1831</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7133</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2753</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B11" t="n">
+        <v>7087</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1468</v>
+      </c>
+      <c r="D11" t="n">
+        <v>480</v>
+      </c>
+      <c r="E11" t="n">
+        <v>391</v>
+      </c>
+      <c r="F11" t="n">
         <v>180</v>
       </c>
-      <c r="L4" t="n">
+      <c r="G11" t="n">
+        <v>77</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2150</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7747</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B12" t="n">
+        <v>7180</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D12" t="n">
+        <v>447</v>
+      </c>
+      <c r="E12" t="n">
+        <v>408</v>
+      </c>
+      <c r="F12" t="n">
         <v>179</v>
       </c>
-      <c r="M4" t="n">
+      <c r="G12" t="n">
+        <v>71</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2276</v>
+      </c>
+      <c r="I12" t="n">
+        <v>7806</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3051</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B13" t="n">
+        <v>7271</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1568</v>
+      </c>
+      <c r="D13" t="n">
+        <v>435</v>
+      </c>
+      <c r="E13" t="n">
+        <v>289</v>
+      </c>
+      <c r="F13" t="n">
         <v>145</v>
       </c>
-      <c r="N4" t="n">
+      <c r="G13" t="n">
+        <v>40</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2019</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7850</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3355</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B14" t="n">
+        <v>7165</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1401</v>
+      </c>
+      <c r="D14" t="n">
+        <v>415</v>
+      </c>
+      <c r="E14" t="n">
+        <v>286</v>
+      </c>
+      <c r="F14" t="n">
         <v>144</v>
       </c>
-      <c r="O4" t="n">
+      <c r="G14" t="n">
+        <v>38</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2068</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7724</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3372</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B15" t="n">
+        <v>7238</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1322</v>
+      </c>
+      <c r="D15" t="n">
+        <v>397</v>
+      </c>
+      <c r="E15" t="n">
+        <v>279</v>
+      </c>
+      <c r="F15" t="n">
         <v>125</v>
       </c>
-      <c r="P4" t="n">
+      <c r="G15" t="n">
+        <v>40</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2168</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7760</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3430</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B16" t="n">
+        <v>7829</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D16" t="n">
+        <v>335</v>
+      </c>
+      <c r="E16" t="n">
+        <v>264</v>
+      </c>
+      <c r="F16" t="n">
         <v>157</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="G16" t="n">
+        <v>38</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2002</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8321</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3574</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B17" t="n">
+        <v>7820</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2053</v>
+      </c>
+      <c r="D17" t="n">
+        <v>338</v>
+      </c>
+      <c r="E17" t="n">
+        <v>282</v>
+      </c>
+      <c r="F17" t="n">
         <v>204</v>
       </c>
-      <c r="R4" t="n">
+      <c r="G17" t="n">
+        <v>41</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2083</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8363</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3362</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8033</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2170</v>
+      </c>
+      <c r="D18" t="n">
+        <v>366</v>
+      </c>
+      <c r="E18" t="n">
+        <v>279</v>
+      </c>
+      <c r="F18" t="n">
         <v>284</v>
       </c>
-      <c r="S4" t="n">
+      <c r="G18" t="n">
+        <v>43</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2067</v>
+      </c>
+      <c r="I18" t="n">
+        <v>8683</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3474</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8693</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2533</v>
+      </c>
+      <c r="D19" t="n">
+        <v>379</v>
+      </c>
+      <c r="E19" t="n">
+        <v>281</v>
+      </c>
+      <c r="F19" t="n">
         <v>250</v>
       </c>
-      <c r="T4" t="n">
+      <c r="G19" t="n">
+        <v>33</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2109</v>
+      </c>
+      <c r="I19" t="n">
+        <v>9322</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3737</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8672</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2333</v>
+      </c>
+      <c r="D20" t="n">
+        <v>523</v>
+      </c>
+      <c r="E20" t="n">
+        <v>309</v>
+      </c>
+      <c r="F20" t="n">
         <v>318</v>
       </c>
-      <c r="U4" t="n">
+      <c r="G20" t="n">
+        <v>49</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2162</v>
+      </c>
+      <c r="I20" t="n">
+        <v>9512</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3819</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B21" t="n">
+        <v>9163</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2713</v>
+      </c>
+      <c r="D21" t="n">
+        <v>537</v>
+      </c>
+      <c r="E21" t="n">
+        <v>300</v>
+      </c>
+      <c r="F21" t="n">
         <v>333</v>
       </c>
-      <c r="V4" t="n">
+      <c r="G21" t="n">
+        <v>43</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2177</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10032</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3930</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B22" t="n">
+        <v>9707</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2945</v>
+      </c>
+      <c r="D22" t="n">
+        <v>647</v>
+      </c>
+      <c r="E22" t="n">
+        <v>317</v>
+      </c>
+      <c r="F22" t="n">
         <v>325</v>
       </c>
-      <c r="W4" t="n">
+      <c r="G22" t="n">
+        <v>48</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2359</v>
+      </c>
+      <c r="I22" t="n">
+        <v>10680</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4040</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B23" t="n">
+        <v>9915</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3034</v>
+      </c>
+      <c r="D23" t="n">
+        <v>565</v>
+      </c>
+      <c r="E23" t="n">
+        <v>358</v>
+      </c>
+      <c r="F23" t="n">
         <v>319</v>
       </c>
-      <c r="X4" t="n">
+      <c r="G23" t="n">
+        <v>48</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2365</v>
+      </c>
+      <c r="I23" t="n">
+        <v>10799</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4110</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B24" t="n">
+        <v>10254</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3488</v>
+      </c>
+      <c r="D24" t="n">
+        <v>552</v>
+      </c>
+      <c r="E24" t="n">
+        <v>348</v>
+      </c>
+      <c r="F24" t="n">
         <v>490</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="G24" t="n">
+        <v>51</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2498</v>
+      </c>
+      <c r="I24" t="n">
+        <v>11296</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3868</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B25" t="n">
+        <v>10640</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3219</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1375</v>
+      </c>
+      <c r="E25" t="n">
+        <v>350</v>
+      </c>
+      <c r="F25" t="n">
         <v>490</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="G25" t="n">
+        <v>55</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2912</v>
+      </c>
+      <c r="I25" t="n">
+        <v>12505</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4104</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B26" t="n">
+        <v>11108</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3741</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1603</v>
+      </c>
+      <c r="E26" t="n">
+        <v>327</v>
+      </c>
+      <c r="F26" t="n">
         <v>567</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="G26" t="n">
+        <v>53</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2914</v>
+      </c>
+      <c r="I26" t="n">
+        <v>13277</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4073</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B27" t="n">
+        <v>12191</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4055</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1312</v>
+      </c>
+      <c r="E27" t="n">
+        <v>384</v>
+      </c>
+      <c r="F27" t="n">
         <v>619</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="G27" t="n">
+        <v>57</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3178</v>
+      </c>
+      <c r="I27" t="n">
+        <v>14122</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4517</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B28" t="n">
+        <v>13012</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4879</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1405</v>
+      </c>
+      <c r="E28" t="n">
+        <v>403</v>
+      </c>
+      <c r="F28" t="n">
         <v>556</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="G28" t="n">
+        <v>58</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3410</v>
+      </c>
+      <c r="I28" t="n">
+        <v>14973</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4261</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B29" t="n">
+        <v>13596</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4943</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1485</v>
+      </c>
+      <c r="E29" t="n">
+        <v>428</v>
+      </c>
+      <c r="F29" t="n">
         <v>563</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="G29" t="n">
+        <v>71</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3472</v>
+      </c>
+      <c r="I29" t="n">
+        <v>15643</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4683</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B30" t="n">
+        <v>14354</v>
+      </c>
+      <c r="C30" t="n">
+        <v>5077</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1483</v>
+      </c>
+      <c r="E30" t="n">
+        <v>437</v>
+      </c>
+      <c r="F30" t="n">
         <v>556</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="G30" t="n">
+        <v>65</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3602</v>
+      </c>
+      <c r="I30" t="n">
+        <v>16394</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5174</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B31" t="n">
+        <v>15314</v>
+      </c>
+      <c r="C31" t="n">
+        <v>5764</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1530</v>
+      </c>
+      <c r="E31" t="n">
+        <v>474</v>
+      </c>
+      <c r="F31" t="n">
         <v>539</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="G31" t="n">
+        <v>86</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3530</v>
+      </c>
+      <c r="I31" t="n">
+        <v>17383</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5460</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B32" t="n">
+        <v>16566</v>
+      </c>
+      <c r="C32" t="n">
+        <v>6723</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1509</v>
+      </c>
+      <c r="E32" t="n">
+        <v>513</v>
+      </c>
+      <c r="F32" t="n">
         <v>558</v>
+      </c>
+      <c r="G32" t="n">
+        <v>90</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3758</v>
+      </c>
+      <c r="I32" t="n">
+        <v>18632</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5482</v>
       </c>
     </row>
   </sheetData>
